--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2605AFFB-1C48-4BE4-86E8-FDCF2F599555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CD3864-85F1-4BB6-BF73-F24BC1411B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="15640" windowWidth="19200" windowHeight="11250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -512,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="16" max="16" width="17.25" customWidth="1"/>
@@ -751,11 +751,6 @@
       </c>
       <c r="Q10" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="B11">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CD3864-85F1-4BB6-BF73-F24BC1411B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC407B11-F59E-48D5-B3B4-733A4CEBFEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC407B11-F59E-48D5-B3B4-733A4CEBFEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5AAB99-A5D8-48C5-ABAA-6DA59ED4E560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -151,6 +151,30 @@
   </si>
   <si>
     <t>周围食材,FALSE</t>
+  </si>
+  <si>
+    <t>左移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_方向位移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>食材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -512,10 +536,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="16" max="16" width="17.25" customWidth="1"/>
+    <col min="15" max="15" width="12.5" customWidth="1"/>
+    <col min="16" max="16" width="22.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
@@ -751,6 +776,35 @@
       </c>
       <c r="Q10" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="s">
+        <v>38</v>
+      </c>
+      <c r="P11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>39</v>
+      </c>
+      <c r="R11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5AAB99-A5D8-48C5-ABAA-6DA59ED4E560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66489E99-1DAF-456F-B1AF-067E2F44DEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -174,6 +174,22 @@
   </si>
   <si>
     <t>食材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创造地形</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意格子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_修改地块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -536,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="12.5" customWidth="1"/>
@@ -805,6 +821,29 @@
       </c>
       <c r="R11" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="s">
+        <v>44</v>
+      </c>
+      <c r="P12" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66489E99-1DAF-456F-B1AF-067E2F44DEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CC25C8-BFC2-42B1-9F70-9B043825E497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -190,6 +190,22 @@
   </si>
   <si>
     <t>Ice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建实体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空格子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_创建实体</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -552,14 +568,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:R13"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="15" max="15" width="12.5" customWidth="1"/>
-    <col min="16" max="16" width="22.375" customWidth="1"/>
+    <col min="16" max="16" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -591,7 +607,7 @@
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -623,7 +639,7 @@
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -642,7 +658,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -663,7 +679,7 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -684,7 +700,7 @@
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>1</v>
       </c>
@@ -710,7 +726,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2</v>
       </c>
@@ -739,7 +755,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>3</v>
       </c>
@@ -765,7 +781,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>4</v>
       </c>
@@ -794,7 +810,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>5</v>
       </c>
@@ -823,7 +839,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>6</v>
       </c>
@@ -844,6 +860,32 @@
       </c>
       <c r="P12" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
+        <v>49</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CC25C8-BFC2-42B1-9F70-9B043825E497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CF7F24-0A06-4B8A-8D13-F4E7B00AF9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -206,6 +206,10 @@
   </si>
   <si>
     <t>GA_创建实体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -569,13 +573,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="12.5" customWidth="1"/>
-    <col min="16" max="16" width="22.33203125" customWidth="1"/>
+    <col min="16" max="16" width="22.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -607,7 +611,7 @@
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -639,7 +643,7 @@
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -658,7 +662,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -679,7 +683,7 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -700,7 +704,7 @@
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1</v>
       </c>
@@ -726,7 +730,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>2</v>
       </c>
@@ -755,7 +759,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>3</v>
       </c>
@@ -778,10 +782,10 @@
         <v>31</v>
       </c>
       <c r="P9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>4</v>
       </c>
@@ -810,7 +814,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>5</v>
       </c>
@@ -839,7 +843,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>6</v>
       </c>
@@ -862,7 +866,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>7</v>
       </c>

--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CF7F24-0A06-4B8A-8D13-F4E7B00AF9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC1FA2A-03E2-4A8A-9747-97D2916C0762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -210,6 +210,18 @@
   </si>
   <si>
     <t>DV_值,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_抽牌</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -572,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="12.5" customWidth="1"/>
@@ -717,6 +729,9 @@
       <c r="E7" t="s">
         <v>20</v>
       </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
       <c r="I7" t="s">
         <v>21</v>
       </c>
@@ -743,6 +758,9 @@
       <c r="E8" s="4" t="s">
         <v>26</v>
       </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
       <c r="I8" t="s">
         <v>21</v>
       </c>
@@ -772,6 +790,9 @@
       <c r="E9" t="s">
         <v>20</v>
       </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
       <c r="I9" t="s">
         <v>21</v>
       </c>
@@ -798,6 +819,9 @@
       <c r="E10" t="s">
         <v>33</v>
       </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
       <c r="I10" t="s">
         <v>21</v>
       </c>
@@ -824,6 +848,9 @@
       <c r="E11" t="s">
         <v>41</v>
       </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
       <c r="I11" t="s">
         <v>37</v>
       </c>
@@ -853,6 +880,9 @@
       <c r="E12" t="s">
         <v>43</v>
       </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
       <c r="I12" t="s">
         <v>37</v>
       </c>
@@ -879,6 +909,9 @@
       <c r="E13" t="s">
         <v>48</v>
       </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
       <c r="I13" t="s">
         <v>37</v>
       </c>
@@ -890,6 +923,35 @@
       </c>
       <c r="P13">
         <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="I14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC1FA2A-03E2-4A8A-9747-97D2916C0762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A56CF2-7064-459A-8B17-052FBF71E8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="63">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -222,6 +222,42 @@
   </si>
   <si>
     <t>GA_抽牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复制食材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定点爆破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挤开周围的食材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选取,false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_定点爆破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请离</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立刻让一个顾客离开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意顾客</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择一个食材，在随机位置生成其原始复制</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -584,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="12.5" customWidth="1"/>
@@ -893,6 +929,9 @@
         <v>44</v>
       </c>
       <c r="P12" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q12" t="s">
         <v>45</v>
       </c>
     </row>
@@ -952,6 +991,81 @@
       </c>
       <c r="P14" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="I15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="I16" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="O16" t="s">
+        <v>58</v>
+      </c>
+      <c r="P16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A56CF2-7064-459A-8B17-052FBF71E8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9717F8F1-D537-4682-A08C-BE668D3358DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="69">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -258,6 +258,30 @@
   </si>
   <si>
     <t>选择一个食材，在随机位置生成其原始复制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_使顾客离开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选取,DV_值-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方向移动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择一个食材，使其向一个方向移动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_效果选择</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card_移动_向上|Card_移动_向下|Card_移动_向左|Card_移动_向右</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -620,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="12.5" customWidth="1"/>
@@ -1045,7 +1069,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>11</v>
       </c>
@@ -1066,6 +1090,41 @@
       </c>
       <c r="J17">
         <v>1</v>
+      </c>
+      <c r="O17" t="s">
+        <v>63</v>
+      </c>
+      <c r="P17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="I18" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="P18" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9717F8F1-D537-4682-A08C-BE668D3358DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036C55BE-E41D-4EDF-AFD5-9CB731E58FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036C55BE-E41D-4EDF-AFD5-9CB731E58FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BDCE43-7C96-4EF4-A797-E0CD93506526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="73">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -282,6 +282,22 @@
   </si>
   <si>
     <t>Card_移动_向上|Card_移动_向下|Card_移动_向左|Card_移动_向右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>##</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽两张牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交换两个相邻食材的位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽取3张食材卡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -645,13 +661,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="4" max="4" width="22" customWidth="1"/>
     <col min="15" max="15" width="12.5" customWidth="1"/>
-    <col min="16" max="16" width="22.375" customWidth="1"/>
+    <col min="16" max="16" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -683,7 +700,7 @@
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -715,7 +732,7 @@
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -734,7 +751,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -755,7 +772,7 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -776,7 +793,10 @@
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>69</v>
+      </c>
       <c r="B7">
         <v>1</v>
       </c>
@@ -805,7 +825,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2</v>
       </c>
@@ -837,7 +857,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>3</v>
       </c>
@@ -845,7 +865,7 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -866,7 +886,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>4</v>
       </c>
@@ -874,7 +894,7 @@
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -898,7 +918,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>5</v>
       </c>
@@ -930,7 +950,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>6</v>
       </c>
@@ -959,7 +979,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>7</v>
       </c>
@@ -988,7 +1008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>8</v>
       </c>
@@ -996,13 +1016,13 @@
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
         <v>52</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="s">
         <v>37</v>
@@ -1017,7 +1037,10 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
       <c r="B15">
         <v>9</v>
       </c>
@@ -1031,7 +1054,7 @@
         <v>41</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="s">
         <v>37</v>
@@ -1040,7 +1063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>10</v>
       </c>
@@ -1054,7 +1077,7 @@
         <v>43</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="s">
         <v>37</v>
@@ -1069,7 +1092,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>11</v>
       </c>
@@ -1098,7 +1121,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>12</v>
       </c>
@@ -1112,7 +1135,7 @@
         <v>41</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="s">
         <v>37</v>

--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BDCE43-7C96-4EF4-A797-E0CD93506526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4ACB11-6580-490D-8BED-28DCCF8C77BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/CardDatas/CardData.xlsx
+++ b/Config/Datas/CardDatas/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CardDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4ACB11-6580-490D-8BED-28DCCF8C77BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF151FA-9FED-4280-AEB2-38E9235D289F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="74">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -132,9 +132,6 @@
     <t>选取,DV_值~1,棋盘上</t>
   </si>
   <si>
-    <t>周围空位,FALSE</t>
-  </si>
-  <si>
     <t>补充</t>
   </si>
   <si>
@@ -150,9 +147,6 @@
     <t>GA_食材换位</t>
   </si>
   <si>
-    <t>周围食材,FALSE</t>
-  </si>
-  <si>
     <t>左移</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -237,10 +231,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>选取,false</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GA_定点爆破</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -298,6 +288,22 @@
   </si>
   <si>
     <t>抽取3张食材卡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选取,有实体,false,GS_周围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选取,空格,false,GS_周围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选取,任意,false,GS_1x1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选取,任意,false,GS_实心周围</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -795,7 +801,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -854,7 +860,7 @@
         <v>28</v>
       </c>
       <c r="Q8" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -862,10 +868,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -880,10 +886,10 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -891,13 +897,13 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
         <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -909,13 +915,13 @@
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P10" t="s">
         <v>28</v>
       </c>
       <c r="Q10" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -923,31 +929,31 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="s">
         <v>36</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="O11" t="s">
-        <v>38</v>
       </c>
       <c r="P11" t="s">
         <v>28</v>
       </c>
       <c r="Q11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -955,28 +961,28 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="s">
         <v>42</v>
       </c>
-      <c r="E12" t="s">
+      <c r="P12" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q12" t="s">
         <v>43</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="O12" t="s">
-        <v>44</v>
-      </c>
-      <c r="P12" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -984,25 +990,25 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" t="s">
         <v>46</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
         <v>47</v>
-      </c>
-      <c r="E13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="O13" t="s">
-        <v>49</v>
       </c>
       <c r="P13">
         <v>1</v>
@@ -1013,51 +1019,51 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="O14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="I14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="P14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B15">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1068,28 +1074,28 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="O16" t="s">
         <v>55</v>
       </c>
-      <c r="D16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="I16" t="s">
-        <v>37</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="O16" t="s">
-        <v>58</v>
-      </c>
       <c r="P16" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
@@ -1097,28 +1103,28 @@
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="s">
         <v>60</v>
       </c>
-      <c r="E17" t="s">
+      <c r="P17" t="s">
         <v>61</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="I17" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="O17" t="s">
-        <v>63</v>
-      </c>
-      <c r="P17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
@@ -1126,28 +1132,28 @@
         <v>12</v>
       </c>
       <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P18" t="s">
         <v>65</v>
-      </c>
-      <c r="D18" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="I18" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="P18" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
